--- a/scripts/output/scopus_6089491.xlsx
+++ b/scripts/output/scopus_6089491.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,25 +453,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Profile Photo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Bidang Minat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SINTA Score Overall</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SINTA Score 3Yr</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Affil Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Affil Score 3Yr</t>
         </is>
@@ -498,23 +503,28 @@
           <t>6089491</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://scholar.googleusercontent.com/citations?view_op=view_photo&amp;user=vRI8v3cAAAAJ&amp;citpid=1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
